--- a/03_Outputs/all/idx10_juventud_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx10_juventud_loadings_y_tops.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,7 +387,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -396,19 +396,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.1935875419291221</v>
+        <v>0.2848369323248398</v>
       </c>
       <c r="D2">
-        <v>0.06416080646274064</v>
+        <v>0.08756561138303522</v>
       </c>
       <c r="E2">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -417,19 +417,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.0924220132335889</v>
+        <v>0.2379559714563001</v>
       </c>
       <c r="D3">
-        <v>0.03063146959192366</v>
+        <v>0.0731532949493077</v>
       </c>
       <c r="E3">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.3600777830647492</v>
+        <v>0.1585680418029529</v>
       </c>
       <c r="D4">
-        <v>0.1193407422839673</v>
+        <v>0.04874756729387575</v>
       </c>
       <c r="E4">
-        <v>11.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.2558907002753369</v>
+        <v>0.3752156752646145</v>
       </c>
       <c r="D5">
-        <v>0.08480997037501627</v>
+        <v>0.1153501750523491</v>
       </c>
       <c r="E5">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.4156195354973412</v>
+        <v>0.2451323432026471</v>
       </c>
       <c r="D6">
-        <v>0.1377489703802449</v>
+        <v>0.07535948139553776</v>
       </c>
       <c r="E6">
-        <v>13.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -501,19 +501,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.2018038600552163</v>
+        <v>0.4253471914402677</v>
       </c>
       <c r="D7">
-        <v>0.06688394449048442</v>
+        <v>0.1307617890858596</v>
       </c>
       <c r="E7">
-        <v>6.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.09105033154092727</v>
+        <v>0.1486645826555254</v>
       </c>
       <c r="D8">
-        <v>0.03017685250895264</v>
+        <v>0.04570300966585578</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -543,19 +543,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.4755859297326909</v>
+        <v>0.04920367080159427</v>
       </c>
       <c r="D9">
-        <v>0.1576236595077682</v>
+        <v>0.01512637241548983</v>
       </c>
       <c r="E9">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.4562411110892471</v>
+        <v>0.4099142983612811</v>
       </c>
       <c r="D10">
-        <v>0.151212197526949</v>
+        <v>0.1260173526574779</v>
       </c>
       <c r="E10">
-        <v>15.1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.0387124798336036</v>
+        <v>0.3934296527244887</v>
       </c>
       <c r="D11">
-        <v>0.01283049467721424</v>
+        <v>0.1209495826115198</v>
       </c>
       <c r="E11">
-        <v>1.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.1628660264652042</v>
+        <v>-0.08105247315225404</v>
       </c>
       <c r="D12">
-        <v>0.05397876071599413</v>
+        <v>0.02491744770509604</v>
       </c>
       <c r="E12">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -627,40 +627,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.2733669492869415</v>
+        <v>-0.1827648003987826</v>
       </c>
       <c r="D13">
-        <v>0.0906021314787445</v>
+        <v>0.05618622330887301</v>
       </c>
       <c r="E13">
-        <v>9.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PC2</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C14">
-        <v>-0.2739200239008849</v>
+        <v>0.2607544691219797</v>
       </c>
       <c r="D14">
-        <v>0.08655957565665363</v>
+        <v>0.08016209247572258</v>
       </c>
       <c r="E14">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.4294601143329365</v>
+        <v>-0.1736915605605251</v>
       </c>
       <c r="D15">
-        <v>0.1357107258123192</v>
+        <v>0.05393075177861881</v>
       </c>
       <c r="E15">
-        <v>13.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.1792614975933746</v>
+        <v>-0.2492495053889323</v>
       </c>
       <c r="D16">
-        <v>0.05664718826424069</v>
+        <v>0.07739128580970925</v>
       </c>
       <c r="E16">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -711,19 +711,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.06146231850959996</v>
+        <v>-0.4145503740937822</v>
       </c>
       <c r="D17">
-        <v>0.01942228294704772</v>
+        <v>0.128716750847516</v>
       </c>
       <c r="E17">
-        <v>1.9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.1833558757750009</v>
+        <v>-0.1138886058908639</v>
       </c>
       <c r="D18">
-        <v>0.05794102444654066</v>
+        <v>0.03536209885438175</v>
       </c>
       <c r="E18">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.3172777259464664</v>
+        <v>0.09769543047975815</v>
       </c>
       <c r="D19">
-        <v>0.1002607437460342</v>
+        <v>0.03033416243199202</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.3436379724144119</v>
+        <v>-0.1035464107677408</v>
       </c>
       <c r="D20">
-        <v>0.1085906632458068</v>
+        <v>0.03215087571705014</v>
       </c>
       <c r="E20">
-        <v>10.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.2610140433413993</v>
+        <v>0.342655356975583</v>
       </c>
       <c r="D21">
-        <v>0.08248124584069857</v>
+        <v>0.1063935457947866</v>
       </c>
       <c r="E21">
-        <v>8.199999999999999</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.2171657404485108</v>
+        <v>0.339301041792377</v>
       </c>
       <c r="D22">
-        <v>0.06862504636458361</v>
+        <v>0.1053520401571555</v>
       </c>
       <c r="E22">
-        <v>6.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.4489641000569745</v>
+        <v>0.3494756133340251</v>
       </c>
       <c r="D23">
-        <v>0.1418740456888429</v>
+        <v>0.1085112166335233</v>
       </c>
       <c r="E23">
-        <v>14.2</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.3560069790692604</v>
+        <v>0.3062450736348645</v>
       </c>
       <c r="D24">
-        <v>0.112499307645332</v>
+        <v>0.09508825297168939</v>
       </c>
       <c r="E24">
-        <v>11.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -879,61 +879,61 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.09299956455409525</v>
+        <v>0.4094015108995303</v>
       </c>
       <c r="D25">
-        <v>0.02938815034190001</v>
+        <v>0.1271180429887394</v>
       </c>
       <c r="E25">
-        <v>2.9</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C26">
-        <v>-0.5886501800040881</v>
+        <v>0.2928502578731172</v>
       </c>
       <c r="D26">
-        <v>0.2173985872848656</v>
+        <v>0.09092919952294456</v>
       </c>
       <c r="E26">
-        <v>21.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC2</t>
         </is>
       </c>
       <c r="C27">
-        <v>-0.5022114557935464</v>
+        <v>-0.02808970614679319</v>
       </c>
       <c r="D27">
-        <v>0.185475286879271</v>
+        <v>0.008721776491893285</v>
       </c>
       <c r="E27">
-        <v>18.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -942,19 +942,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.01280977337633485</v>
+        <v>-0.1499377123747034</v>
       </c>
       <c r="D28">
-        <v>0.004730868570251926</v>
+        <v>0.0517416630881565</v>
       </c>
       <c r="E28">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.02239773905925201</v>
+        <v>-0.5398949865219262</v>
       </c>
       <c r="D29">
-        <v>0.008271868412276076</v>
+        <v>0.1863111291560251</v>
       </c>
       <c r="E29">
-        <v>0.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.1067102907715973</v>
+        <v>-0.4500463850051689</v>
       </c>
       <c r="D30">
-        <v>0.03940993692101032</v>
+        <v>0.155305480243601</v>
       </c>
       <c r="E30">
-        <v>3.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.2288742431464953</v>
+        <v>0.01269075790564952</v>
       </c>
       <c r="D31">
-        <v>0.08452717558940584</v>
+        <v>0.004379424692344853</v>
       </c>
       <c r="E31">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.2345942973339397</v>
+        <v>-0.02680650037103778</v>
       </c>
       <c r="D32">
-        <v>0.08663968950987158</v>
+        <v>0.009250594055380481</v>
       </c>
       <c r="E32">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.170170375042834</v>
+        <v>0.132322006760915</v>
       </c>
       <c r="D33">
-        <v>0.06284683227615924</v>
+        <v>0.04566269942722658</v>
       </c>
       <c r="E33">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1068,19 +1068,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.1192646892797705</v>
+        <v>-0.225750502716333</v>
       </c>
       <c r="D34">
-        <v>0.04404649118124875</v>
+        <v>0.07790372594414188</v>
       </c>
       <c r="E34">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.3582009989360375</v>
+        <v>-0.2526484239709368</v>
       </c>
       <c r="D35">
-        <v>0.1322897601631267</v>
+        <v>0.08718586822366009</v>
       </c>
       <c r="E35">
-        <v>13.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.3304557304839792</v>
+        <v>0.1807397646425076</v>
       </c>
       <c r="D36">
-        <v>0.1220429576134784</v>
+        <v>0.06237107303194461</v>
       </c>
       <c r="E36">
-        <v>12.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1131,82 +1131,82 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.03336034274738439</v>
+        <v>0.1400288121341443</v>
       </c>
       <c r="D37">
-        <v>0.01232054559903458</v>
+        <v>0.04832222331079158</v>
       </c>
       <c r="E37">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C38">
-        <v>-0.06920569183751743</v>
+        <v>-0.3947081516762114</v>
       </c>
       <c r="D38">
-        <v>0.02297664077974413</v>
+        <v>0.1362089355554629</v>
       </c>
       <c r="E38">
-        <v>2.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C39">
-        <v>-0.1622143101345408</v>
+        <v>-0.3768290229363322</v>
       </c>
       <c r="D39">
-        <v>0.05385597389945915</v>
+        <v>0.1300390678089367</v>
       </c>
       <c r="E39">
-        <v>5.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC3</t>
         </is>
       </c>
       <c r="C40">
-        <v>0.3352532987391441</v>
+        <v>0.01541090910060966</v>
       </c>
       <c r="D40">
-        <v>0.111305795966014</v>
+        <v>0.005318115462327678</v>
       </c>
       <c r="E40">
-        <v>11.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.4511805480162749</v>
+        <v>-0.1185071527381705</v>
       </c>
       <c r="D41">
-        <v>0.1497942308403909</v>
+        <v>0.03888824983124947</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1236,19 +1236,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.1585540607837799</v>
+        <v>-0.005503431443513909</v>
       </c>
       <c r="D42">
-        <v>0.05264075254607426</v>
+        <v>0.001805956956685776</v>
       </c>
       <c r="E42">
-        <v>5.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1257,19 +1257,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.421445326209357</v>
+        <v>-0.1197028421473867</v>
       </c>
       <c r="D43">
-        <v>0.1399219863497552</v>
+        <v>0.03928061659892394</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1278,19 +1278,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.5016192623939192</v>
+        <v>0.2784593009897116</v>
       </c>
       <c r="D44">
-        <v>0.166540139896082</v>
+        <v>0.09137671958626939</v>
       </c>
       <c r="E44">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.1959258465671294</v>
+        <v>-0.5303848906999634</v>
       </c>
       <c r="D45">
-        <v>0.06504837501819104</v>
+        <v>0.1740463732331044</v>
       </c>
       <c r="E45">
-        <v>6.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.2801640882836569</v>
+        <v>0.09010731222023005</v>
       </c>
       <c r="D46">
-        <v>0.0930158986198934</v>
+        <v>0.02956881157194531</v>
       </c>
       <c r="E46">
-        <v>9.300000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1341,19 +1341,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.225406803021725</v>
+        <v>0.424611028238809</v>
       </c>
       <c r="D47">
-        <v>0.07483620212193379</v>
+        <v>0.1393365663230215</v>
       </c>
       <c r="E47">
-        <v>7.5</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.1711154799275273</v>
+        <v>0.4654779312978802</v>
       </c>
       <c r="D48">
-        <v>0.05681120742755005</v>
+        <v>0.1527470845851713</v>
       </c>
       <c r="E48">
-        <v>5.7</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1383,103 +1383,103 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.03991745189266335</v>
+        <v>-0.1675952780771593</v>
       </c>
       <c r="D49">
-        <v>0.01325279653491207</v>
+        <v>0.05499657104075417</v>
       </c>
       <c r="E49">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C50">
-        <v>-0.1054784205463985</v>
+        <v>-0.2154547746827451</v>
       </c>
       <c r="D50">
-        <v>0.0425371530572464</v>
+        <v>0.07070171640786908</v>
       </c>
       <c r="E50">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C51">
-        <v>0.02982513808739951</v>
+        <v>-0.219630173701526</v>
       </c>
       <c r="D51">
-        <v>0.01202782955229358</v>
+        <v>0.07207187809377387</v>
       </c>
       <c r="E51">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C52">
-        <v>0.2368517149287524</v>
+        <v>-0.2119279319850279</v>
       </c>
       <c r="D52">
-        <v>0.09551714556973087</v>
+        <v>0.06954437917736983</v>
       </c>
       <c r="E52">
-        <v>9.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PC5</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="C53">
-        <v>0.5072554707891014</v>
+        <v>0.2000148137456152</v>
       </c>
       <c r="D53">
-        <v>0.2045650995559805</v>
+        <v>0.06563507659386193</v>
       </c>
       <c r="E53">
-        <v>20.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1488,19 +1488,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.3340906471042145</v>
+        <v>0.3257540532485929</v>
       </c>
       <c r="D54">
-        <v>0.1347314921597175</v>
+        <v>0.1061828777363576</v>
       </c>
       <c r="E54">
-        <v>13.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1509,19 +1509,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.01930432392545801</v>
+        <v>-0.2131690728306186</v>
       </c>
       <c r="D55">
-        <v>0.007785014007890443</v>
+        <v>0.06948464761011856</v>
       </c>
       <c r="E55">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1530,19 +1530,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.09293684200404764</v>
+        <v>-0.1318498063969931</v>
       </c>
       <c r="D56">
-        <v>0.03747940718589272</v>
+        <v>0.04297779792023142</v>
       </c>
       <c r="E56">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1551,19 +1551,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>-0.08838929557522732</v>
+        <v>0.2832225869224498</v>
       </c>
       <c r="D57">
-        <v>0.03564548061138004</v>
+        <v>0.09231930967382768</v>
       </c>
       <c r="E57">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>-0.2172698443836645</v>
+        <v>0.2902029221013911</v>
       </c>
       <c r="D58">
-        <v>0.08762020304623921</v>
+        <v>0.09459462158314316</v>
       </c>
       <c r="E58">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>-0.03764170982538283</v>
+        <v>0.3128654826396339</v>
       </c>
       <c r="D59">
-        <v>0.0151800829390921</v>
+        <v>0.1019817158366985</v>
       </c>
       <c r="E59">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.1146695784051319</v>
+        <v>0.06275337104963442</v>
       </c>
       <c r="D60">
-        <v>0.04624374713198683</v>
+        <v>0.02045510549832704</v>
       </c>
       <c r="E60">
-        <v>4.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1635,124 +1635,124 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.6959644955308766</v>
+        <v>0.2075630135153894</v>
       </c>
       <c r="D61">
-        <v>0.2806673451825498</v>
+        <v>0.0676572950264272</v>
       </c>
       <c r="E61">
-        <v>28.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C62">
-        <v>-0.008984281841910087</v>
+        <v>-0.1358773439453483</v>
       </c>
       <c r="D62">
-        <v>0.003300956470416092</v>
+        <v>0.04429061512944429</v>
       </c>
       <c r="E62">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C63">
-        <v>0.07907396522766606</v>
+        <v>-0.2865231254020314</v>
       </c>
       <c r="D63">
-        <v>0.02905293063515779</v>
+        <v>0.09339515407344932</v>
       </c>
       <c r="E63">
-        <v>2.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C64">
-        <v>-0.4757961985250712</v>
+        <v>-0.06154213023257419</v>
       </c>
       <c r="D64">
-        <v>0.174814477969093</v>
+        <v>0.02006028911982125</v>
       </c>
       <c r="E64">
-        <v>17.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C65">
-        <v>0.4808912904055844</v>
+        <v>0.1221407250859994</v>
       </c>
       <c r="D65">
-        <v>0.1766864892000729</v>
+        <v>0.03981302319679658</v>
       </c>
       <c r="E65">
-        <v>17.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PC6</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="C66">
-        <v>-0.177486199517884</v>
+        <v>-0.6343949535609443</v>
       </c>
       <c r="D66">
-        <v>0.06521102398804109</v>
+        <v>0.2067875475953574</v>
       </c>
       <c r="E66">
-        <v>6.5</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1761,19 +1761,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.3303384997125364</v>
+        <v>0.3944299906285705</v>
       </c>
       <c r="D67">
-        <v>0.1213711932952687</v>
+        <v>0.1358656839579023</v>
       </c>
       <c r="E67">
-        <v>12.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.2137029320453137</v>
+        <v>-0.06296227170597286</v>
       </c>
       <c r="D68">
-        <v>0.07851758089235247</v>
+        <v>0.0216880366912334</v>
       </c>
       <c r="E68">
-        <v>7.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1803,19 +1803,19 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.06487680846754558</v>
+        <v>-0.1962017590814461</v>
       </c>
       <c r="D69">
-        <v>0.02383668772409748</v>
+        <v>0.06758382178004023</v>
       </c>
       <c r="E69">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1824,19 +1824,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.1372824563758316</v>
+        <v>0.3071863541115333</v>
       </c>
       <c r="D70">
-        <v>0.05043958110647073</v>
+        <v>0.1058136680666359</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>-0.08912283980136425</v>
+        <v>-0.5390852829702274</v>
       </c>
       <c r="D71">
-        <v>0.03274503403620119</v>
+        <v>0.1856937667586271</v>
       </c>
       <c r="E71">
-        <v>3.3</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="C72">
-        <v>-0.5536432360403757</v>
+        <v>0.04145944719844284</v>
       </c>
       <c r="D72">
-        <v>0.2034166174289384</v>
+        <v>0.01428115580449717</v>
       </c>
       <c r="E72">
-        <v>20.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1887,145 +1887,145 @@
         </is>
       </c>
       <c r="C73">
-        <v>0.1105220788560785</v>
+        <v>-0.349979509160022</v>
       </c>
       <c r="D73">
-        <v>0.04060742725389013</v>
+        <v>0.1205542339909308</v>
       </c>
       <c r="E73">
-        <v>4.1</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C74">
-        <v>-0.02697080762336233</v>
+        <v>-0.1479265821507652</v>
       </c>
       <c r="D74">
-        <v>0.009676654404680086</v>
+        <v>0.05095491402020363</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C75">
-        <v>-0.1243244529881581</v>
+        <v>0.04201801537178943</v>
       </c>
       <c r="D75">
-        <v>0.04460544090549276</v>
+        <v>0.01447356066394488</v>
       </c>
       <c r="E75">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C76">
-        <v>-0.05013204156429043</v>
+        <v>0.1072951606525297</v>
       </c>
       <c r="D76">
-        <v>0.01798650035227308</v>
+        <v>0.0369589806398789</v>
       </c>
       <c r="E76">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C77">
-        <v>0.2863828041210326</v>
+        <v>0.1191855081495715</v>
       </c>
       <c r="D77">
-        <v>0.1027491449874851</v>
+        <v>0.04105473966826376</v>
       </c>
       <c r="E77">
-        <v>10.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C78">
-        <v>0.152760437985633</v>
+        <v>0.47960469398226</v>
       </c>
       <c r="D78">
-        <v>0.05480777534500293</v>
+        <v>0.1652050334039691</v>
       </c>
       <c r="E78">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PC7</t>
+          <t>PC6</t>
         </is>
       </c>
       <c r="C79">
-        <v>-0.5453756588174207</v>
+        <v>0.1157530856680159</v>
       </c>
       <c r="D79">
-        <v>0.1956712548173589</v>
+        <v>0.03987240455387285</v>
       </c>
       <c r="E79">
-        <v>19.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2034,19 +2034,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.5305929451584717</v>
+        <v>-0.6047881598356682</v>
       </c>
       <c r="D80">
-        <v>0.1903674755149889</v>
+        <v>0.2012303563770841</v>
       </c>
       <c r="E80">
-        <v>19</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2055,19 +2055,19 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.1316912819199959</v>
+        <v>0.1392996395765517</v>
       </c>
       <c r="D81">
-        <v>0.04724853037568141</v>
+        <v>0.04634898296091889</v>
       </c>
       <c r="E81">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2076,19 +2076,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>-0.1247863913736229</v>
+        <v>0.1898213546340991</v>
       </c>
       <c r="D82">
-        <v>0.04477117632486995</v>
+        <v>0.06315900571099087</v>
       </c>
       <c r="E82">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2097,19 +2097,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.1321015969250495</v>
+        <v>0.3374664840534334</v>
       </c>
       <c r="D83">
-        <v>0.04739574422839227</v>
+        <v>0.1122847723570612</v>
       </c>
       <c r="E83">
-        <v>4.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2118,19 +2118,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>0.2573672358037752</v>
+        <v>-0.2309878727075213</v>
       </c>
       <c r="D84">
-        <v>0.09233886618225286</v>
+        <v>0.07685628626782141</v>
       </c>
       <c r="E84">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2139,166 +2139,166 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.4247181142363289</v>
+        <v>0.1418662029977269</v>
       </c>
       <c r="D85">
-        <v>0.1523814365615217</v>
+        <v>0.04720295217891383</v>
       </c>
       <c r="E85">
-        <v>15.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C86">
-        <v>-0.3114591689006315</v>
+        <v>0.1196890414689053</v>
       </c>
       <c r="D86">
-        <v>0.1002560629689204</v>
+        <v>0.03982397485387903</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C87">
-        <v>-0.05395990099460891</v>
+        <v>-0.3189111873176559</v>
       </c>
       <c r="D87">
-        <v>0.01736923414715133</v>
+        <v>0.1061108932655168</v>
       </c>
       <c r="E87">
-        <v>1.7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C88">
-        <v>0.328089074332539</v>
+        <v>0.1235913966528072</v>
       </c>
       <c r="D88">
-        <v>0.1056090883816365</v>
+        <v>0.0411224002803621</v>
       </c>
       <c r="E88">
-        <v>10.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C89">
-        <v>0.27469512665376</v>
+        <v>0.1800971076800444</v>
       </c>
       <c r="D89">
-        <v>0.0884220298033393</v>
+        <v>0.05992347001433489</v>
       </c>
       <c r="E89">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C90">
-        <v>0.06309063483771959</v>
+        <v>-0.01271541481946901</v>
       </c>
       <c r="D90">
-        <v>0.02030833987442376</v>
+        <v>0.004230782984077363</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C91">
-        <v>0.2344877596053316</v>
+        <v>0.1551593024884112</v>
       </c>
       <c r="D91">
-        <v>0.07547961960925122</v>
+        <v>0.05162594741181205</v>
       </c>
       <c r="E91">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PC8</t>
+          <t>PC7</t>
         </is>
       </c>
       <c r="C92">
-        <v>-0.3848003338092083</v>
+        <v>-0.4510587503007201</v>
       </c>
       <c r="D92">
-        <v>0.1238639614720919</v>
+        <v>0.1500801753372273</v>
       </c>
       <c r="E92">
-        <v>12.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2307,19 +2307,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>-0.2410277022419945</v>
+        <v>0.386037876998599</v>
       </c>
       <c r="D93">
-        <v>0.07758477163642943</v>
+        <v>0.141346599612448</v>
       </c>
       <c r="E93">
-        <v>7.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2328,19 +2328,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.3286400029484839</v>
+        <v>-0.1245994529507261</v>
       </c>
       <c r="D94">
-        <v>0.1057864276271193</v>
+        <v>0.04562171236948401</v>
       </c>
       <c r="E94">
-        <v>10.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2349,19 +2349,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>0.3446616094598666</v>
+        <v>0.0006001464543200774</v>
       </c>
       <c r="D95">
-        <v>0.110943646780237</v>
+        <v>0.0002197418068069993</v>
       </c>
       <c r="E95">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2370,19 +2370,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.07297135870429011</v>
+        <v>0.001422149755045773</v>
       </c>
       <c r="D96">
-        <v>0.02348886102473047</v>
+        <v>0.0005207158260693821</v>
       </c>
       <c r="E96">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2391,187 +2391,187 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.4687540702408762</v>
+        <v>-0.1732992131470613</v>
       </c>
       <c r="D97">
-        <v>0.1508879566746694</v>
+        <v>0.06345298208636366</v>
       </c>
       <c r="E97">
-        <v>15.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C98">
-        <v>-0.0252426841277318</v>
+        <v>-0.2083965008593142</v>
       </c>
       <c r="D98">
-        <v>0.01013103909786366</v>
+        <v>0.07630374769598987</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C99">
-        <v>0.02965925106694865</v>
+        <v>0.5515705590591991</v>
       </c>
       <c r="D99">
-        <v>0.01190360861198999</v>
+        <v>0.2019558898611332</v>
       </c>
       <c r="E99">
-        <v>1.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C100">
-        <v>-0.5679365168248367</v>
+        <v>-0.52741143483166</v>
       </c>
       <c r="D100">
-        <v>0.2279387971557181</v>
+        <v>0.193110099687052</v>
       </c>
       <c r="E100">
-        <v>22.8</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C101">
-        <v>-0.1416446304163615</v>
+        <v>0.02391225493799694</v>
       </c>
       <c r="D101">
-        <v>0.0568484429583341</v>
+        <v>0.008755399731317308</v>
       </c>
       <c r="E101">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C102">
-        <v>0.6541400896514612</v>
+        <v>-0.03727983527225701</v>
       </c>
       <c r="D102">
-        <v>0.2625362180267665</v>
+        <v>0.01364989878924459</v>
       </c>
       <c r="E102">
-        <v>26.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C103">
-        <v>0.2525782445047273</v>
+        <v>0.2658119516911069</v>
       </c>
       <c r="D103">
-        <v>0.1013711559911315</v>
+        <v>0.09732624114504344</v>
       </c>
       <c r="E103">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C104">
-        <v>-0.1815736084601673</v>
+        <v>-0.2996027907578097</v>
       </c>
       <c r="D104">
-        <v>0.07287376085450528</v>
+        <v>0.1096986545394608</v>
       </c>
       <c r="E104">
-        <v>7.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PC9</t>
+          <t>PC8</t>
         </is>
       </c>
       <c r="C105">
-        <v>-0.004050298193063678</v>
+        <v>-0.1311995470853003</v>
       </c>
       <c r="D105">
-        <v>0.001625569180531586</v>
+        <v>0.04803831684958669</v>
       </c>
       <c r="E105">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2580,19 +2580,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.09351364242972927</v>
+        <v>0.2521176498511719</v>
       </c>
       <c r="D106">
-        <v>0.03753128482079366</v>
+        <v>0.07703297242517576</v>
       </c>
       <c r="E106">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2601,19 +2601,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.1423602100490729</v>
+        <v>0.2689240206660368</v>
       </c>
       <c r="D107">
-        <v>0.05713563766393476</v>
+        <v>0.08216805400440282</v>
       </c>
       <c r="E107">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2622,19 +2622,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.3057801727374897</v>
+        <v>0.01937553110247814</v>
       </c>
       <c r="D108">
-        <v>0.1227235134615367</v>
+        <v>0.005920072450387377</v>
       </c>
       <c r="E108">
-        <v>12.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2643,208 +2643,208 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.09313912067004528</v>
+        <v>-0.3805085137680741</v>
       </c>
       <c r="D109">
-        <v>0.03738097217689416</v>
+        <v>0.1162619985786149</v>
       </c>
       <c r="E109">
-        <v>3.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C110">
-        <v>0.00334450236672636</v>
+        <v>-0.3382580013714392</v>
       </c>
       <c r="D110">
-        <v>0.001352636236847188</v>
+        <v>0.1033526185398877</v>
       </c>
       <c r="E110">
-        <v>0.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C111">
-        <v>-0.01732392803596499</v>
+        <v>-0.1490136602441663</v>
       </c>
       <c r="D111">
-        <v>0.007006415381585052</v>
+        <v>0.04553019269908134</v>
       </c>
       <c r="E111">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C112">
-        <v>-0.1019507876054316</v>
+        <v>-0.1004981266634903</v>
       </c>
       <c r="D112">
-        <v>0.04123254062014568</v>
+        <v>0.03070657458777866</v>
       </c>
       <c r="E112">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C113">
-        <v>-0.208084471231385</v>
+        <v>0.2715715026531825</v>
       </c>
       <c r="D113">
-        <v>0.08415679382169389</v>
+        <v>0.08297697558142186</v>
       </c>
       <c r="E113">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C114">
-        <v>0.3915386664764073</v>
+        <v>0.248644365990947</v>
       </c>
       <c r="D114">
-        <v>0.1583522241370701</v>
+        <v>0.07597173224628527</v>
       </c>
       <c r="E114">
-        <v>15.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C115">
-        <v>-0.3058052499114124</v>
+        <v>0.3106695815759007</v>
       </c>
       <c r="D115">
-        <v>0.1236785677186307</v>
+        <v>0.09492314927179629</v>
       </c>
       <c r="E115">
-        <v>12.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C116">
-        <v>0.1141278226624148</v>
+        <v>-0.2582246228822607</v>
       </c>
       <c r="D116">
-        <v>0.04615736861228615</v>
+        <v>0.07889891987226193</v>
       </c>
       <c r="E116">
-        <v>4.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C117">
-        <v>-0.07263835688706796</v>
+        <v>-0.1865019479194767</v>
       </c>
       <c r="D117">
-        <v>0.02937754647387442</v>
+        <v>0.05698450473341915</v>
       </c>
       <c r="E117">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PC10</t>
+          <t>PC9</t>
         </is>
       </c>
       <c r="C118">
-        <v>-0.02671625754109901</v>
+        <v>-0.4885461886490068</v>
       </c>
       <c r="D118">
-        <v>0.01080500896712003</v>
+        <v>0.1492722350094869</v>
       </c>
       <c r="E118">
-        <v>1.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2853,19 +2853,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.6715561361611321</v>
+        <v>0.009546864264675626</v>
       </c>
       <c r="D119">
-        <v>0.2716012922836579</v>
+        <v>0.00401282322115996</v>
       </c>
       <c r="E119">
-        <v>27.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2874,19 +2874,19 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.470346630423488</v>
+        <v>-0.02460502177992623</v>
       </c>
       <c r="D120">
-        <v>0.1902249801104222</v>
+        <v>0.01034220242566623</v>
       </c>
       <c r="E120">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2895,229 +2895,229 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.08914797451703008</v>
+        <v>0.025310890100949</v>
       </c>
       <c r="D121">
-        <v>0.03605462563666667</v>
+        <v>0.01063889930027898</v>
       </c>
       <c r="E121">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C122">
-        <v>0.6506423107857301</v>
+        <v>-0.5786918223306456</v>
       </c>
       <c r="D122">
-        <v>0.3280347041255247</v>
+        <v>0.2432409132636484</v>
       </c>
       <c r="E122">
-        <v>32.8</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C123">
-        <v>-0.6894338507508957</v>
+        <v>-0.1670244774763168</v>
       </c>
       <c r="D123">
-        <v>0.3475922569069901</v>
+        <v>0.07020521955036359</v>
       </c>
       <c r="E123">
-        <v>34.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C124">
-        <v>0.006289622173466236</v>
+        <v>0.6933786015045033</v>
       </c>
       <c r="D124">
-        <v>0.003171042390776512</v>
+        <v>0.2914470841978842</v>
       </c>
       <c r="E124">
-        <v>0.3</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C125">
-        <v>0.1020172627250472</v>
+        <v>0.2157994762472153</v>
       </c>
       <c r="D125">
-        <v>0.05143410140864257</v>
+        <v>0.09070676249196738</v>
       </c>
       <c r="E125">
-        <v>5.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C126">
-        <v>0.01785172311577646</v>
+        <v>-0.1671986826578703</v>
       </c>
       <c r="D126">
-        <v>0.009000313403139587</v>
+        <v>0.07027844302756027</v>
       </c>
       <c r="E126">
-        <v>0.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C127">
-        <v>0.01154201413667918</v>
+        <v>-0.01173068422045556</v>
       </c>
       <c r="D127">
-        <v>0.005819143836136173</v>
+        <v>0.004930745921895455</v>
       </c>
       <c r="E127">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C128">
-        <v>-0.1910097202805789</v>
+        <v>-0.09635859441341099</v>
       </c>
       <c r="D128">
-        <v>0.09630147938223071</v>
+        <v>0.04050230468355862</v>
       </c>
       <c r="E128">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C129">
-        <v>0.03050554861495916</v>
+        <v>-0.06174436512467277</v>
       </c>
       <c r="D129">
-        <v>0.01537999980666859</v>
+        <v>0.02595294279660364</v>
       </c>
       <c r="E129">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C130">
-        <v>-0.2250483802093874</v>
+        <v>0.2464761475731312</v>
       </c>
       <c r="D130">
-        <v>0.1134627699307841</v>
+        <v>0.1036010548618725</v>
       </c>
       <c r="E130">
-        <v>11.3</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PC11</t>
+          <t>PC10</t>
         </is>
       </c>
       <c r="C131">
-        <v>-0.001592818385777587</v>
+        <v>0.0812235418301165</v>
       </c>
       <c r="D131">
-        <v>0.0008030521520699513</v>
+        <v>0.0341406042575408</v>
       </c>
       <c r="E131">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3126,19 +3126,19 @@
         </is>
       </c>
       <c r="C132">
-        <v>-0.04783393768642023</v>
+        <v>-0.09031606297565209</v>
       </c>
       <c r="D132">
-        <v>0.0241164635868433</v>
+        <v>0.03696045743896759</v>
       </c>
       <c r="E132">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3147,264 +3147,789 @@
         </is>
       </c>
       <c r="C133">
-        <v>-0.009688532749289575</v>
+        <v>0.00549258361481722</v>
       </c>
       <c r="D133">
-        <v>0.004884673070193709</v>
+        <v>0.002247755230209169</v>
       </c>
       <c r="E133">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C134">
-        <v>-0.05717318999731746</v>
+        <v>-0.0005333760588397893</v>
       </c>
       <c r="D134">
-        <v>0.02965684734174819</v>
+        <v>0.0002182759353341926</v>
       </c>
       <c r="E134">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C135">
-        <v>0.1627361586793944</v>
+        <v>-0.009050619896578141</v>
       </c>
       <c r="D135">
-        <v>0.08441441548326682</v>
+        <v>0.003703826766385179</v>
       </c>
       <c r="E135">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tránsito inmediato a ed. sup.</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C136">
-        <v>-0.005348994985795073</v>
+        <v>-0.1728272475979236</v>
       </c>
       <c r="D136">
-        <v>0.002774627893474968</v>
+        <v>0.07072688864725005</v>
       </c>
       <c r="E136">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C137">
-        <v>-0.08288454601717792</v>
+        <v>0.3337989739039353</v>
       </c>
       <c r="D137">
-        <v>0.04299382854685704</v>
+        <v>0.1366020878420423</v>
       </c>
       <c r="E137">
-        <v>4.3</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C138">
-        <v>-0.07183306210248863</v>
+        <v>-0.3430069198572028</v>
       </c>
       <c r="D138">
-        <v>0.03726120856582915</v>
+        <v>0.1403702978734938</v>
       </c>
       <c r="E138">
-        <v>3.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C139">
-        <v>-0.09617341636256246</v>
+        <v>0.1380487404176544</v>
       </c>
       <c r="D139">
-        <v>0.04988702445206795</v>
+        <v>0.05649432035235328</v>
       </c>
       <c r="E139">
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C140">
-        <v>0.02410796010307667</v>
+        <v>-0.07969880377835739</v>
       </c>
       <c r="D140">
-        <v>0.01250526851014342</v>
+        <v>0.03261550767310049</v>
       </c>
       <c r="E140">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C141">
-        <v>0.7380127773891101</v>
+        <v>-0.011854395108</v>
       </c>
       <c r="D141">
-        <v>0.3828216035578103</v>
+        <v>0.004851228579040884</v>
       </c>
       <c r="E141">
-        <v>38.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C142">
-        <v>-0.6342185908385413</v>
+        <v>0.6792727733994238</v>
       </c>
       <c r="D142">
-        <v>0.3289815371624319</v>
+        <v>0.2779819182048177</v>
       </c>
       <c r="E142">
-        <v>32.9</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C143">
-        <v>0.03094433628576597</v>
+        <v>-0.4870822336554063</v>
       </c>
       <c r="D143">
-        <v>0.01605143000349883</v>
+        <v>0.1993309005414818</v>
       </c>
       <c r="E143">
-        <v>1.6</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PC12</t>
+          <t>PC11</t>
         </is>
       </c>
       <c r="C144">
-        <v>0.001995076665975066</v>
+        <v>-0.09260344896004696</v>
       </c>
       <c r="D144">
-        <v>0.001034885129213231</v>
+        <v>0.03789653491552356</v>
       </c>
       <c r="E144">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>Cobertura bruta ed. superior</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>0.05286283902986642</v>
+      </c>
+      <c r="D145">
+        <v>0.02584919196639438</v>
+      </c>
+      <c r="E145">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Cobertura bruta media</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>-0.6559129290242971</v>
+      </c>
+      <c r="D146">
+        <v>0.3207322861719542</v>
+      </c>
+      <c r="E146">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cobertura bruta secundaria</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>0.6839041044402755</v>
+      </c>
+      <c r="D147">
+        <v>0.3344195810651371</v>
+      </c>
+      <c r="E147">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Tránsito inmediato a ed. sup.</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>-0.01798195022050617</v>
+      </c>
+      <c r="D148">
+        <v>0.00879292318971742</v>
+      </c>
+      <c r="E148">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>% jóvenes 15–28 NiNi</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>-0.1086179789903774</v>
+      </c>
+      <c r="D149">
+        <v>0.05311267880141228</v>
+      </c>
+      <c r="E149">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>% colegios en C–D</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>-0.0316277148077205</v>
+      </c>
+      <c r="D150">
+        <v>0.01546551200288811</v>
+      </c>
+      <c r="E150">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Deserción intraanual (media)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>-0.005199126033541588</v>
+      </c>
+      <c r="D151">
+        <v>0.002542300212490776</v>
+      </c>
+      <c r="E151">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Deserción intraanual (secundaria)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>0.189302042250055</v>
+      </c>
+      <c r="D152">
+        <v>0.09256606189818055</v>
+      </c>
+      <c r="E152">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Fecundidad 15–19 x100k</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>-0.02093226372157055</v>
+      </c>
+      <c r="D153">
+        <v>0.01023558539722714</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Fecundidad niñas 10–14 x100k</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>0.2176642064546499</v>
+      </c>
+      <c r="D154">
+        <v>0.1064347651415452</v>
+      </c>
+      <c r="E154">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Repitencia (media)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>-0.003092330401816598</v>
+      </c>
+      <c r="D155">
+        <v>0.00151210649384369</v>
+      </c>
+      <c r="E155">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Repitencia (secundaria)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PC12</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.04860358949671167</v>
+      </c>
+      <c r="D156">
+        <v>0.02376647827118233</v>
+      </c>
+      <c r="E156">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
           <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>PC12</t>
         </is>
       </c>
-      <c r="C145">
-        <v>0.02239615788236438</v>
-      </c>
-      <c r="D145">
-        <v>0.01161732335365815</v>
-      </c>
-      <c r="E145">
+      <c r="C157">
+        <v>0.009346952107231715</v>
+      </c>
+      <c r="D157">
+        <v>0.004570529388026657</v>
+      </c>
+      <c r="E157">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Cobertura bruta ed. superior</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>-0.03291346982515234</v>
+      </c>
+      <c r="D158">
+        <v>0.01699374787918713</v>
+      </c>
+      <c r="E158">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Cobertura bruta media</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>-0.04714409853738425</v>
+      </c>
+      <c r="D159">
+        <v>0.02434124778675335</v>
+      </c>
+      <c r="E159">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Cobertura bruta secundaria</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0.1596260470448017</v>
+      </c>
+      <c r="D160">
+        <v>0.08241746655217834</v>
+      </c>
+      <c r="E160">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Tránsito inmediato a ed. sup.</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0.001259380310480566</v>
+      </c>
+      <c r="D161">
+        <v>0.0006502380816733015</v>
+      </c>
+      <c r="E161">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>% jóvenes 15–28 NiNi</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>-0.07834251124085008</v>
+      </c>
+      <c r="D162">
+        <v>0.04044948440021327</v>
+      </c>
+      <c r="E162">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>% colegios en C–D</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>-0.06457264097504482</v>
+      </c>
+      <c r="D163">
+        <v>0.03333988140577642</v>
+      </c>
+      <c r="E163">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Deserción intraanual (media)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>-0.09949410710997626</v>
+      </c>
+      <c r="D164">
+        <v>0.05137038971198626</v>
+      </c>
+      <c r="E164">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Deserción intraanual (secundaria)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0.02284354213299858</v>
+      </c>
+      <c r="D165">
+        <v>0.01179448407408895</v>
+      </c>
+      <c r="E165">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Fecundidad 15–19 x100k</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0.7377367686182028</v>
+      </c>
+      <c r="D166">
+        <v>0.3809052255415287</v>
+      </c>
+      <c r="E166">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Fecundidad niñas 10–14 x100k</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>-0.6361186420622696</v>
+      </c>
+      <c r="D167">
+        <v>0.3284381708122461</v>
+      </c>
+      <c r="E167">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Repitencia (media)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0.03263864290341019</v>
+      </c>
+      <c r="D168">
+        <v>0.01685185036903978</v>
+      </c>
+      <c r="E168">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Repitencia (secundaria)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0.001433027695392488</v>
+      </c>
+      <c r="D169">
+        <v>0.0007398949879414544</v>
+      </c>
+      <c r="E169">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Vinc. NNA en grupos armados</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0.02267588183767839</v>
+      </c>
+      <c r="D170">
+        <v>0.01170791839738706</v>
+      </c>
+      <c r="E170">
         <v>1.2</v>
       </c>
     </row>
@@ -3415,7 +3940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3437,7 +3962,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.2410656745558732</v>
+        <v>0.2354548440071243</v>
       </c>
     </row>
     <row r="3">
@@ -3447,7 +3972,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1930237682263269</v>
+        <v>0.1829753541683553</v>
       </c>
     </row>
     <row r="4">
@@ -3457,7 +3982,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.1372421095017249</v>
+        <v>0.1285957321891894</v>
       </c>
     </row>
     <row r="5">
@@ -3467,7 +3992,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.09394634795914376</v>
+        <v>0.08689942468614172</v>
       </c>
     </row>
     <row r="6">
@@ -3477,7 +4002,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.087326623243535</v>
+        <v>0.08484706681061857</v>
       </c>
     </row>
     <row r="7">
@@ -3487,7 +4012,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.06565286490895349</v>
+        <v>0.06328714963326296</v>
       </c>
     </row>
     <row r="8">
@@ -3497,7 +4022,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.05212779062129218</v>
+        <v>0.05324961663690795</v>
       </c>
     </row>
     <row r="9">
@@ -3507,7 +4032,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.04698719947283268</v>
+        <v>0.04608618103809956</v>
       </c>
     </row>
     <row r="10">
@@ -3517,7 +4042,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.03106991697500457</v>
+        <v>0.04275498467388202</v>
       </c>
     </row>
     <row r="11">
@@ -3527,7 +4052,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.0308431950148551</v>
+        <v>0.02867445048967943</v>
       </c>
     </row>
     <row r="12">
@@ -3537,7 +4062,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.01464012723173069</v>
+        <v>0.02823948990916988</v>
       </c>
     </row>
     <row r="13">
@@ -3547,7 +4072,17 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.006074382288727399</v>
+        <v>0.01338648739411115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PC13</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.005549218363457821</v>
       </c>
     </row>
   </sheetData>
@@ -3580,11 +4115,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>% colegios en C–D</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.4755859297326909</v>
+        <v>0.4253471914402677</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3595,11 +4130,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.4562411110892471</v>
+        <v>0.4099142983612811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3610,11 +4145,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.4156195354973412</v>
+        <v>0.3934296527244887</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3629,7 +4164,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3600777830647492</v>
+        <v>0.3752156752646145</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3640,11 +4175,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vinc. NNA en grupos armados</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.2733669492869415</v>
+        <v>0.2848369323248398</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3655,11 +4190,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>% jóvenes 15–28 NiNi</t>
+          <t>Vinc. NNA en grupos armados</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.2558907002753369</v>
+        <v>0.2607544691219797</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3670,11 +4205,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>% jóvenes 15–28 NiNi</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.2018038600552163</v>
+        <v>0.2451323432026471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3689,7 +4224,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.1935875419291221</v>
+        <v>0.2379559714563001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3704,7 +4239,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.1628660264652042</v>
+        <v>-0.1827648003987826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3719,7 +4254,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.0924220132335889</v>
+        <v>0.1585680418029529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3757,41 +4292,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.4489641000569745</v>
+        <v>-0.4145503740937822</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.4294601143329365</v>
+        <v>0.4094015108995303</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Fecundidad 15–19 x100k</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.3560069790692604</v>
+        <v>0.3494756133340251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3802,11 +4337,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.3436379724144119</v>
+        <v>0.342655356975583</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3817,11 +4352,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.3172777259464664</v>
+        <v>0.339301041792377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3832,26 +4367,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Fecundidad niñas 10–14 x100k</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.2739200239008849</v>
+        <v>0.3062450736348645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fecundidad 15–19 x100k</t>
+          <t>Repitencia (secundaria)</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.2610140433413993</v>
+        <v>0.2928502578731172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3862,26 +4397,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fecundidad niñas 10–14 x100k</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.2171657404485108</v>
+        <v>-0.2492495053889323</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>% colegios en C–D</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="B10">
-        <v>-0.1833558757750009</v>
+        <v>-0.1736915605605251</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3896,7 +4431,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.1792614975933746</v>
+        <v>-0.1138886058908639</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
